--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,6 +2101,980 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120090190</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>754533</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7093071</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120090182</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>754465</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7093048</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120090001</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>754478</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7093072</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120090072</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>754496</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7093071</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120090227</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Amerika, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>754101</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7092887</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120090140</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>754497</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7093049</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120089991</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>754472</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7093069</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120090197</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>754568</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7093117</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120090216</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Amerika, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>754093</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7092874</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2209,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090182</v>
+        <v>120090001</v>
       </c>
       <c r="B17" t="n">
         <v>91832</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754465</v>
+        <v>754478</v>
       </c>
       <c r="R17" t="n">
-        <v>7093048</v>
+        <v>7093072</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090001</v>
+        <v>120090182</v>
       </c>
       <c r="B18" t="n">
         <v>91832</v>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754478</v>
+        <v>754465</v>
       </c>
       <c r="R18" t="n">
-        <v>7093072</v>
+        <v>7093048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090190</v>
+        <v>120090216</v>
       </c>
       <c r="B16" t="n">
         <v>91863</v>
@@ -2142,14 +2142,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754533</v>
+        <v>754093</v>
       </c>
       <c r="R16" t="n">
-        <v>7093071</v>
+        <v>7092874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090001</v>
+        <v>120090140</v>
       </c>
       <c r="B17" t="n">
         <v>91832</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754478</v>
+        <v>754497</v>
       </c>
       <c r="R17" t="n">
-        <v>7093072</v>
+        <v>7093049</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090182</v>
+        <v>120089991</v>
       </c>
       <c r="B18" t="n">
         <v>91832</v>
@@ -2349,7 +2349,11 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754465</v>
+        <v>754472</v>
       </c>
       <c r="R18" t="n">
-        <v>7093048</v>
+        <v>7093069</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090072</v>
+        <v>120090227</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,37 +2441,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754496</v>
+        <v>754101</v>
       </c>
       <c r="R19" t="n">
-        <v>7093071</v>
+        <v>7092887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,7 +2521,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2527,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090227</v>
+        <v>120090197</v>
       </c>
       <c r="B20" t="n">
         <v>57463</v>
@@ -2562,7 +2574,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2575,14 +2587,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754101</v>
+        <v>754568</v>
       </c>
       <c r="R20" t="n">
-        <v>7092887</v>
+        <v>7093117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090140</v>
+        <v>120090190</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2684,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754497</v>
+        <v>754533</v>
       </c>
       <c r="R21" t="n">
-        <v>7093049</v>
+        <v>7093071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,7 +2759,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120089991</v>
+        <v>120090072</v>
       </c>
       <c r="B22" t="n">
         <v>91832</v>
@@ -2781,11 +2793,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2794,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754472</v>
+        <v>754496</v>
       </c>
       <c r="R22" t="n">
-        <v>7093069</v>
+        <v>7093071</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090197</v>
+        <v>120090001</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,35 +2881,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2909,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754568</v>
+        <v>754478</v>
       </c>
       <c r="R23" t="n">
-        <v>7093117</v>
+        <v>7093072</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,6 +2952,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090216</v>
+        <v>120090182</v>
       </c>
       <c r="B24" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,14 +3010,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754093</v>
+        <v>754465</v>
       </c>
       <c r="R24" t="n">
-        <v>7092874</v>
+        <v>7093048</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090216</v>
+        <v>120090182</v>
       </c>
       <c r="B16" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2142,14 +2142,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754093</v>
+        <v>754465</v>
       </c>
       <c r="R16" t="n">
-        <v>7092874</v>
+        <v>7093048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090140</v>
+        <v>120090072</v>
       </c>
       <c r="B17" t="n">
         <v>91832</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754497</v>
+        <v>754496</v>
       </c>
       <c r="R17" t="n">
-        <v>7093049</v>
+        <v>7093071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090227</v>
+        <v>120090140</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,46 +2441,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754101</v>
+        <v>754497</v>
       </c>
       <c r="R19" t="n">
-        <v>7092887</v>
+        <v>7093049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,6 +2512,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2759,10 +2751,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090072</v>
+        <v>120090216</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,21 +2767,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2798,14 +2790,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754496</v>
+        <v>754093</v>
       </c>
       <c r="R22" t="n">
-        <v>7093071</v>
+        <v>7092874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090182</v>
+        <v>120090227</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>57463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,37 +2979,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754465</v>
+        <v>754101</v>
       </c>
       <c r="R24" t="n">
-        <v>7093048</v>
+        <v>7092887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,7 +3059,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090182</v>
+        <v>120090190</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754465</v>
+        <v>754533</v>
       </c>
       <c r="R16" t="n">
-        <v>7093048</v>
+        <v>7093071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090072</v>
+        <v>120090182</v>
       </c>
       <c r="B17" t="n">
         <v>91832</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754496</v>
+        <v>754465</v>
       </c>
       <c r="R17" t="n">
-        <v>7093071</v>
+        <v>7093048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120089991</v>
+        <v>120090197</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,30 +2331,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754472</v>
+        <v>754568</v>
       </c>
       <c r="R18" t="n">
-        <v>7093069</v>
+        <v>7093117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,7 +2411,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2425,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090140</v>
+        <v>120090072</v>
       </c>
       <c r="B19" t="n">
         <v>91832</v>
@@ -2468,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754497</v>
+        <v>754496</v>
       </c>
       <c r="R19" t="n">
-        <v>7093049</v>
+        <v>7093071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090197</v>
+        <v>120089991</v>
       </c>
       <c r="B20" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,35 +2551,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2583,10 +2582,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754568</v>
+        <v>754472</v>
       </c>
       <c r="R20" t="n">
-        <v>7093117</v>
+        <v>7093069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,6 +2626,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090190</v>
+        <v>120090216</v>
       </c>
       <c r="B21" t="n">
         <v>91863</v>
@@ -2684,14 +2684,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754533</v>
+        <v>754093</v>
       </c>
       <c r="R21" t="n">
-        <v>7093071</v>
+        <v>7092874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090216</v>
+        <v>120090227</v>
       </c>
       <c r="B22" t="n">
-        <v>91863</v>
+        <v>57463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,26 +2767,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2794,10 +2803,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754093</v>
+        <v>754101</v>
       </c>
       <c r="R22" t="n">
-        <v>7092874</v>
+        <v>7092887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,7 +2847,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2857,7 +2865,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090001</v>
+        <v>120090140</v>
       </c>
       <c r="B23" t="n">
         <v>91832</v>
@@ -2900,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754478</v>
+        <v>754497</v>
       </c>
       <c r="R23" t="n">
-        <v>7093072</v>
+        <v>7093049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090227</v>
+        <v>120090001</v>
       </c>
       <c r="B24" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,46 +2987,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754101</v>
+        <v>754478</v>
       </c>
       <c r="R24" t="n">
-        <v>7092887</v>
+        <v>7093072</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,6 +3058,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090182</v>
+        <v>120090197</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2225,26 +2225,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754465</v>
+        <v>754568</v>
       </c>
       <c r="R17" t="n">
-        <v>7093048</v>
+        <v>7093117</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2305,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090197</v>
+        <v>120090182</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,35 +2339,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2367,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754568</v>
+        <v>754465</v>
       </c>
       <c r="R18" t="n">
-        <v>7093117</v>
+        <v>7093048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,6 +2410,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090190</v>
+        <v>120090227</v>
       </c>
       <c r="B16" t="n">
-        <v>91863</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,37 +2119,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754533</v>
+        <v>754101</v>
       </c>
       <c r="R16" t="n">
-        <v>7093071</v>
+        <v>7092887</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,7 +2199,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090197</v>
+        <v>120090140</v>
       </c>
       <c r="B17" t="n">
-        <v>57463</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2225,35 +2233,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2261,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754568</v>
+        <v>754497</v>
       </c>
       <c r="R17" t="n">
-        <v>7093117</v>
+        <v>7093049</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2304,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090182</v>
+        <v>120090190</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754465</v>
+        <v>754533</v>
       </c>
       <c r="R18" t="n">
-        <v>7093048</v>
+        <v>7093071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090072</v>
+        <v>120090001</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754496</v>
+        <v>754478</v>
       </c>
       <c r="R19" t="n">
-        <v>7093071</v>
+        <v>7093072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120089991</v>
+        <v>120090216</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>91881</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,41 +2551,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754472</v>
+        <v>754093</v>
       </c>
       <c r="R20" t="n">
-        <v>7093069</v>
+        <v>7092874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2645,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090216</v>
+        <v>120090072</v>
       </c>
       <c r="B21" t="n">
-        <v>91863</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2661,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2684,14 +2680,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754093</v>
+        <v>754496</v>
       </c>
       <c r="R21" t="n">
-        <v>7092874</v>
+        <v>7093071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090227</v>
+        <v>120089991</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,46 +2763,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754101</v>
+        <v>754472</v>
       </c>
       <c r="R22" t="n">
-        <v>7092887</v>
+        <v>7093069</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,6 +2838,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2865,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090140</v>
+        <v>120090182</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754497</v>
+        <v>754465</v>
       </c>
       <c r="R23" t="n">
-        <v>7093049</v>
+        <v>7093048</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090001</v>
+        <v>120090197</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,26 +2979,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3014,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754478</v>
+        <v>754568</v>
       </c>
       <c r="R24" t="n">
-        <v>7093072</v>
+        <v>7093117</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,7 +3059,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090227</v>
+        <v>120090190</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,46 +2119,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754101</v>
+        <v>754533</v>
       </c>
       <c r="R16" t="n">
-        <v>7092887</v>
+        <v>7093071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,6 +2190,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2217,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090140</v>
+        <v>120090197</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,26 +2225,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2260,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754497</v>
+        <v>754568</v>
       </c>
       <c r="R17" t="n">
-        <v>7093049</v>
+        <v>7093117</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,7 +2305,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090190</v>
+        <v>120090182</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754533</v>
+        <v>754465</v>
       </c>
       <c r="R18" t="n">
-        <v>7093071</v>
+        <v>7093048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090001</v>
+        <v>120090227</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,37 +2445,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754478</v>
+        <v>754101</v>
       </c>
       <c r="R19" t="n">
-        <v>7093072</v>
+        <v>7092887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,7 +2525,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2535,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090216</v>
+        <v>120089991</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,37 +2559,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754093</v>
+        <v>754472</v>
       </c>
       <c r="R20" t="n">
-        <v>7092874</v>
+        <v>7093069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090072</v>
+        <v>120090001</v>
       </c>
       <c r="B21" t="n">
         <v>91850</v>
@@ -2684,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754496</v>
+        <v>754478</v>
       </c>
       <c r="R21" t="n">
-        <v>7093071</v>
+        <v>7093072</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,17 +2752,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Anna Becker, Severin Suess</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120089991</v>
+        <v>120090216</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,41 +2775,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754472</v>
+        <v>754093</v>
       </c>
       <c r="R22" t="n">
-        <v>7093069</v>
+        <v>7092874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,7 +2865,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090182</v>
+        <v>120090072</v>
       </c>
       <c r="B23" t="n">
         <v>91850</v>
@@ -2900,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754465</v>
+        <v>754496</v>
       </c>
       <c r="R23" t="n">
-        <v>7093048</v>
+        <v>7093071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2956,17 +2964,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Anna Becker, Severin Suess</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090197</v>
+        <v>120090140</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,35 +2987,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3015,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754568</v>
+        <v>754497</v>
       </c>
       <c r="R24" t="n">
-        <v>7093117</v>
+        <v>7093049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,6 +3058,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090197</v>
+        <v>120090182</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2225,35 +2225,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2261,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754568</v>
+        <v>754465</v>
       </c>
       <c r="R17" t="n">
-        <v>7093117</v>
+        <v>7093048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2296,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090182</v>
+        <v>120090197</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,26 +2331,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754465</v>
+        <v>754568</v>
       </c>
       <c r="R18" t="n">
-        <v>7093048</v>
+        <v>7093117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2411,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090190</v>
+        <v>120090227</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,37 +2119,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754533</v>
+        <v>754101</v>
       </c>
       <c r="R16" t="n">
-        <v>7093071</v>
+        <v>7092887</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,7 +2199,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,7 +2217,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090182</v>
+        <v>120090072</v>
       </c>
       <c r="B17" t="n">
         <v>91850</v>
@@ -2252,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754465</v>
+        <v>754496</v>
       </c>
       <c r="R17" t="n">
-        <v>7093048</v>
+        <v>7093071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090227</v>
+        <v>120090001</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,46 +2453,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754101</v>
+        <v>754478</v>
       </c>
       <c r="R19" t="n">
-        <v>7092887</v>
+        <v>7093072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,6 +2524,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090001</v>
+        <v>120090182</v>
       </c>
       <c r="B21" t="n">
         <v>91850</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754478</v>
+        <v>754465</v>
       </c>
       <c r="R21" t="n">
-        <v>7093072</v>
+        <v>7093048</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna Becker, Severin Suess</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090072</v>
+        <v>120090140</v>
       </c>
       <c r="B23" t="n">
         <v>91850</v>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754496</v>
+        <v>754497</v>
       </c>
       <c r="R23" t="n">
-        <v>7093071</v>
+        <v>7093049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,17 +2964,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Becker, Severin Suess</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090140</v>
+        <v>120090190</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754497</v>
+        <v>754533</v>
       </c>
       <c r="R24" t="n">
-        <v>7093049</v>
+        <v>7093071</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090227</v>
+        <v>120090197</v>
       </c>
       <c r="B16" t="n">
         <v>57473</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2151,14 +2151,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754101</v>
+        <v>754568</v>
       </c>
       <c r="R16" t="n">
-        <v>7092887</v>
+        <v>7093117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2217,7 +2217,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090072</v>
+        <v>120090001</v>
       </c>
       <c r="B17" t="n">
         <v>91850</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754496</v>
+        <v>754478</v>
       </c>
       <c r="R17" t="n">
-        <v>7093071</v>
+        <v>7093072</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090197</v>
+        <v>120090190</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,35 +2339,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2375,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754568</v>
+        <v>754533</v>
       </c>
       <c r="R18" t="n">
-        <v>7093117</v>
+        <v>7093071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,6 +2410,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2437,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090001</v>
+        <v>120090182</v>
       </c>
       <c r="B19" t="n">
         <v>91850</v>
@@ -2480,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754478</v>
+        <v>754465</v>
       </c>
       <c r="R19" t="n">
-        <v>7093072</v>
+        <v>7093048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,7 +2535,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120089991</v>
+        <v>120090072</v>
       </c>
       <c r="B20" t="n">
         <v>91850</v>
@@ -2577,11 +2569,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2590,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754472</v>
+        <v>754496</v>
       </c>
       <c r="R20" t="n">
-        <v>7093069</v>
+        <v>7093071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2641,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090182</v>
+        <v>120090140</v>
       </c>
       <c r="B21" t="n">
         <v>91850</v>
@@ -2696,10 +2684,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754465</v>
+        <v>754497</v>
       </c>
       <c r="R21" t="n">
-        <v>7093048</v>
+        <v>7093049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,10 +2747,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090216</v>
+        <v>120090227</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,26 +2763,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2802,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754093</v>
+        <v>754101</v>
       </c>
       <c r="R22" t="n">
-        <v>7092874</v>
+        <v>7092887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2843,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2865,10 +2861,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090140</v>
+        <v>120090216</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,21 +2877,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,14 +2900,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754497</v>
+        <v>754093</v>
       </c>
       <c r="R23" t="n">
-        <v>7093049</v>
+        <v>7092874</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,10 +2967,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090190</v>
+        <v>120089991</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,25 +2983,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754533</v>
+        <v>754472</v>
       </c>
       <c r="R24" t="n">
-        <v>7093071</v>
+        <v>7093069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090197</v>
+        <v>120090072</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,35 +2119,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2155,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754568</v>
+        <v>754496</v>
       </c>
       <c r="R16" t="n">
-        <v>7093117</v>
+        <v>7093071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,6 +2190,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2217,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090001</v>
+        <v>120090227</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,37 +2225,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754478</v>
+        <v>754101</v>
       </c>
       <c r="R17" t="n">
-        <v>7093072</v>
+        <v>7092887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,7 +2305,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090190</v>
+        <v>120090197</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,26 +2339,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2366,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754533</v>
+        <v>754568</v>
       </c>
       <c r="R18" t="n">
-        <v>7093071</v>
+        <v>7093117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2419,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2429,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090182</v>
+        <v>120090190</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2453,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2480,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754465</v>
+        <v>754533</v>
       </c>
       <c r="R19" t="n">
-        <v>7093048</v>
+        <v>7093071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,7 +2543,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090072</v>
+        <v>120090001</v>
       </c>
       <c r="B20" t="n">
         <v>91850</v>
@@ -2578,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754496</v>
+        <v>754478</v>
       </c>
       <c r="R20" t="n">
-        <v>7093071</v>
+        <v>7093072</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,10 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090140</v>
+        <v>120090216</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2665,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2680,14 +2688,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754497</v>
+        <v>754093</v>
       </c>
       <c r="R21" t="n">
-        <v>7093049</v>
+        <v>7092874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2747,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090227</v>
+        <v>120090140</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2763,46 +2771,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754101</v>
+        <v>754497</v>
       </c>
       <c r="R22" t="n">
-        <v>7092887</v>
+        <v>7093049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2843,6 +2842,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090216</v>
+        <v>120089991</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2877,37 +2877,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754093</v>
+        <v>754472</v>
       </c>
       <c r="R23" t="n">
-        <v>7092874</v>
+        <v>7093069</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2967,7 +2971,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120089991</v>
+        <v>120090182</v>
       </c>
       <c r="B24" t="n">
         <v>91850</v>
@@ -3001,11 +3005,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754472</v>
+        <v>754465</v>
       </c>
       <c r="R24" t="n">
-        <v>7093069</v>
+        <v>7093048</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2649,10 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090216</v>
+        <v>120090140</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,14 +2688,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754093</v>
+        <v>754497</v>
       </c>
       <c r="R21" t="n">
-        <v>7092874</v>
+        <v>7093049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090140</v>
+        <v>120090216</v>
       </c>
       <c r="B22" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2794,14 +2794,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754497</v>
+        <v>754093</v>
       </c>
       <c r="R22" t="n">
-        <v>7093049</v>
+        <v>7092874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090072</v>
+        <v>120090197</v>
       </c>
       <c r="B16" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,26 +2119,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2146,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754496</v>
+        <v>754568</v>
       </c>
       <c r="R16" t="n">
-        <v>7093071</v>
+        <v>7093117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,7 +2199,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2217,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090227</v>
+        <v>120090001</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2225,46 +2233,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754101</v>
+        <v>754478</v>
       </c>
       <c r="R17" t="n">
-        <v>7092887</v>
+        <v>7093072</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,6 +2304,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090197</v>
+        <v>120089991</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,35 +2339,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2375,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754568</v>
+        <v>754472</v>
       </c>
       <c r="R18" t="n">
-        <v>7093117</v>
+        <v>7093069</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,6 +2414,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2437,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090190</v>
+        <v>120090182</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2453,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2480,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754533</v>
+        <v>754465</v>
       </c>
       <c r="R19" t="n">
-        <v>7093071</v>
+        <v>7093048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,7 +2539,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090001</v>
+        <v>120090072</v>
       </c>
       <c r="B20" t="n">
         <v>91850</v>
@@ -2586,10 +2582,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754478</v>
+        <v>754496</v>
       </c>
       <c r="R20" t="n">
-        <v>7093072</v>
+        <v>7093071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2755,10 +2751,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090216</v>
+        <v>120090227</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,26 +2767,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2798,10 +2803,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754093</v>
+        <v>754101</v>
       </c>
       <c r="R22" t="n">
-        <v>7092874</v>
+        <v>7092887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2847,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2861,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120089991</v>
+        <v>120090190</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2877,29 +2881,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754472</v>
+        <v>754533</v>
       </c>
       <c r="R23" t="n">
-        <v>7093069</v>
+        <v>7093071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090182</v>
+        <v>120090216</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3010,14 +3010,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754465</v>
+        <v>754093</v>
       </c>
       <c r="R24" t="n">
-        <v>7093048</v>
+        <v>7092874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090197</v>
+        <v>120090190</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,35 +2119,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2155,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754568</v>
+        <v>754533</v>
       </c>
       <c r="R16" t="n">
-        <v>7093117</v>
+        <v>7093071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,6 +2190,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2217,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090001</v>
+        <v>120090072</v>
       </c>
       <c r="B17" t="n">
         <v>91850</v>
@@ -2260,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754478</v>
+        <v>754496</v>
       </c>
       <c r="R17" t="n">
-        <v>7093072</v>
+        <v>7093071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120089991</v>
+        <v>120090001</v>
       </c>
       <c r="B18" t="n">
         <v>91850</v>
@@ -2357,11 +2349,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2370,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754472</v>
+        <v>754478</v>
       </c>
       <c r="R18" t="n">
-        <v>7093069</v>
+        <v>7093072</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090182</v>
+        <v>120090216</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,14 +2460,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754465</v>
+        <v>754093</v>
       </c>
       <c r="R19" t="n">
-        <v>7093048</v>
+        <v>7092874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120090072</v>
+        <v>120090197</v>
       </c>
       <c r="B20" t="n">
-        <v>91850</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,26 +2543,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2582,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754496</v>
+        <v>754568</v>
       </c>
       <c r="R20" t="n">
-        <v>7093071</v>
+        <v>7093117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,7 +2623,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2645,7 +2641,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090140</v>
+        <v>120089991</v>
       </c>
       <c r="B21" t="n">
         <v>91850</v>
@@ -2679,7 +2675,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754497</v>
+        <v>754472</v>
       </c>
       <c r="R21" t="n">
-        <v>7093049</v>
+        <v>7093069</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090227</v>
+        <v>120090140</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,46 +2767,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754101</v>
+        <v>754497</v>
       </c>
       <c r="R22" t="n">
-        <v>7092887</v>
+        <v>7093049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,6 +2838,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2865,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090190</v>
+        <v>120090182</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2881,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754533</v>
+        <v>754465</v>
       </c>
       <c r="R23" t="n">
-        <v>7093071</v>
+        <v>7093048</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090216</v>
+        <v>120090227</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,26 +2979,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3014,10 +3015,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754093</v>
+        <v>754101</v>
       </c>
       <c r="R24" t="n">
-        <v>7092874</v>
+        <v>7092887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,7 +3059,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3075,6 +3075,322 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128730804</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92740</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>754503</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7093050</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, kapad</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128730020</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Amerika, Amerika, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>754185</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7092896</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128730790</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90093</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Amerika, Amerika, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>754322</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7092944</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,48 +3077,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128730804</v>
+        <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92740</v>
+        <v>92792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Amerika, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754503</v>
+        <v>754185</v>
       </c>
       <c r="R25" t="n">
-        <v>7093050</v>
+        <v>7092896</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3145,14 +3145,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, kapad</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3167,22 +3172,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730020</v>
+        <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>92792</v>
+        <v>90093</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,21 +3195,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>4962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754185</v>
+        <v>754322</v>
       </c>
       <c r="R26" t="n">
-        <v>7092896</v>
+        <v>7092944</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3249,7 +3254,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3259,7 +3264,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3286,48 +3291,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128730790</v>
+        <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>90093</v>
+        <v>92740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4962</v>
+        <v>6055</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Amerika, Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754322</v>
+        <v>754503</v>
       </c>
       <c r="R27" t="n">
-        <v>7092944</v>
+        <v>7093050</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3354,19 +3359,14 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:55</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, kapad</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3381,15 +3381,727 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128785519</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>754277</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7092900</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128785495</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90290</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>754090</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7092862</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128785521</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>754553</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7093091</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128785525</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>754167</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7092828</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128785526</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>754472</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7092978</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128785520</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>754483</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7092966</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128785517</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>754150</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7092826</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90093</v>
+        <v>90120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92741</v>
+        <v>92768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90120</v>
+        <v>90125</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92768</v>
+        <v>92773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90125</v>
+        <v>90130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90130</v>
+        <v>90134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92778</v>
+        <v>92782</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90134</v>
+        <v>90139</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92782</v>
+        <v>92787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90146</v>
+        <v>90149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92795</v>
+        <v>92800</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90343</v>
+        <v>90346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90149</v>
+        <v>90152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92800</v>
+        <v>92803</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90346</v>
+        <v>90349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92803</v>
+        <v>92810</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90349</v>
+        <v>90353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92810</v>
+        <v>92817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3080,7 +3080,7 @@
         <v>128730020</v>
       </c>
       <c r="B25" t="n">
-        <v>92864</v>
+        <v>92873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>128730790</v>
       </c>
       <c r="B26" t="n">
-        <v>90156</v>
+        <v>90165</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -3294,7 +3294,7 @@
         <v>128730804</v>
       </c>
       <c r="B27" t="n">
-        <v>92819</v>
+        <v>92805</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>128785495</v>
       </c>
       <c r="B29" t="n">
-        <v>90362</v>
+        <v>90363</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128785520</v>
       </c>
       <c r="B33" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>128785517</v>
       </c>
       <c r="B34" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111674129</v>
+        <v>111674134</v>
       </c>
       <c r="B2" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754111</v>
+        <v>754038</v>
       </c>
       <c r="R2" t="n">
-        <v>7092886</v>
+        <v>7092927</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111674127</v>
+        <v>111674178</v>
       </c>
       <c r="B3" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754126</v>
+        <v>754084</v>
       </c>
       <c r="R3" t="n">
-        <v>7092861</v>
+        <v>7092816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111674180</v>
+        <v>111674181</v>
       </c>
       <c r="B4" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754127</v>
+        <v>754152</v>
       </c>
       <c r="R4" t="n">
-        <v>7092825</v>
+        <v>7092849</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111674181</v>
+        <v>111674124</v>
       </c>
       <c r="B5" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754152</v>
+        <v>754166</v>
       </c>
       <c r="R5" t="n">
-        <v>7092849</v>
+        <v>7092860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111674184</v>
+        <v>111674125</v>
       </c>
       <c r="B6" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754181</v>
+        <v>754155</v>
       </c>
       <c r="R6" t="n">
-        <v>7092889</v>
+        <v>7092859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111674182</v>
+        <v>111674127</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754185</v>
+        <v>754126</v>
       </c>
       <c r="R7" t="n">
-        <v>7092863</v>
+        <v>7092861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1260,7 @@
         <v>111674128</v>
       </c>
       <c r="B8" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111674123</v>
+        <v>111674131</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754176</v>
+        <v>754088</v>
       </c>
       <c r="R9" t="n">
-        <v>7092863</v>
+        <v>7092897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111674131</v>
+        <v>111674180</v>
       </c>
       <c r="B10" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754088</v>
+        <v>754127</v>
       </c>
       <c r="R10" t="n">
-        <v>7092897</v>
+        <v>7092825</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111674183</v>
+        <v>111674184</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754183</v>
+        <v>754181</v>
       </c>
       <c r="R11" t="n">
-        <v>7092867</v>
+        <v>7092889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111674124</v>
+        <v>120089981</v>
       </c>
       <c r="B12" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,16 +1674,23 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Forslundaheden, Umeå, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754166</v>
+        <v>754476</v>
       </c>
       <c r="R12" t="n">
-        <v>7092860</v>
+        <v>7093086</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1717,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1779,33 +1731,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Severin Suess</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111674132</v>
+        <v>120089991</v>
       </c>
       <c r="B13" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1761,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Forslundaheden, Umeå, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754088</v>
+        <v>754472</v>
       </c>
       <c r="R13" t="n">
-        <v>7092899</v>
+        <v>7093069</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1822,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1881,33 +1836,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Severin Suess</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111674125</v>
+        <v>120090001</v>
       </c>
       <c r="B14" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,16 +1884,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Forslundaheden, Umeå, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754155</v>
+        <v>754478</v>
       </c>
       <c r="R14" t="n">
-        <v>7092859</v>
+        <v>7093072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1923,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1983,68 +1937,67 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Severin Suess</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111674121</v>
+        <v>120090072</v>
       </c>
       <c r="B15" t="n">
-        <v>88032</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Forslundaheden, Umeå, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754426</v>
+        <v>754496</v>
       </c>
       <c r="R15" t="n">
-        <v>7092894</v>
+        <v>7093071</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2024,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2085,33 +2038,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Severin Suess</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120090072</v>
+        <v>120090140</v>
       </c>
       <c r="B16" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754496</v>
+        <v>754497</v>
       </c>
       <c r="R16" t="n">
-        <v>7093071</v>
+        <v>7093049</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,15 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120090140</v>
+        <v>120090182</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754497</v>
+        <v>754465</v>
       </c>
       <c r="R17" t="n">
-        <v>7093049</v>
+        <v>7093048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,15 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120090182</v>
+        <v>111674129</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,37 +2270,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Forslundaheden, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754465</v>
+        <v>754111</v>
       </c>
       <c r="R18" t="n">
-        <v>7093048</v>
+        <v>7092886</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,12 +2324,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,81 +2338,63 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Severin Suess</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120090197</v>
+        <v>111674179</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Forslundaheden, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754568</v>
+        <v>754115</v>
       </c>
       <c r="R19" t="n">
-        <v>7093117</v>
+        <v>7092817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,12 +2421,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,27 +2441,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Severin Suess</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120089991</v>
+        <v>128730790</v>
       </c>
       <c r="B20" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,44 +2464,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Amerika, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754472</v>
+        <v>754322</v>
       </c>
       <c r="R20" t="n">
-        <v>7093069</v>
+        <v>7092944</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2612,12 +2518,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,34 +2542,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Severin Suess</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120090001</v>
+        <v>111674123</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,37 +2571,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Forslundaheden, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754478</v>
+        <v>754176</v>
       </c>
       <c r="R21" t="n">
-        <v>7093072</v>
+        <v>7092863</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,12 +2625,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2732,34 +2639,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Severin Suess</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120090227</v>
+        <v>111674182</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,46 +2668,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Forslundaheden, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>754101</v>
+        <v>754185</v>
       </c>
       <c r="R22" t="n">
-        <v>7092887</v>
+        <v>7092863</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,12 +2722,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2853,27 +2742,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Severin Suess</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Severin Suess, Anna Becker</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120090216</v>
+        <v>120090190</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2904,14 +2788,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Amerika, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754093</v>
+        <v>754533</v>
       </c>
       <c r="R23" t="n">
-        <v>7092874</v>
+        <v>7093071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,15 +2855,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120090190</v>
+        <v>120090206</v>
       </c>
       <c r="B24" t="n">
-        <v>91990</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,14 +2889,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>754533</v>
+        <v>754119</v>
       </c>
       <c r="R24" t="n">
-        <v>7093071</v>
+        <v>7092813</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3077,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128730020</v>
+        <v>120090216</v>
       </c>
       <c r="B25" t="n">
-        <v>92873</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3106,19 +2985,22 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Amerika, Amerika, Vb</t>
+          <t>Amerika, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>754185</v>
+        <v>754093</v>
       </c>
       <c r="R25" t="n">
-        <v>7092896</v>
+        <v>7092874</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3142,22 +3024,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3166,28 +3038,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Severin Suess</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Severin Suess, Anna Becker</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128730790</v>
+        <v>128730020</v>
       </c>
       <c r="B26" t="n">
-        <v>90165</v>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,21 +3068,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4962</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3219,10 +3092,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754322</v>
+        <v>754185</v>
       </c>
       <c r="R26" t="n">
-        <v>7092944</v>
+        <v>7092896</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3254,7 +3127,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3264,7 +3137,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3291,45 +3164,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128730804</v>
+        <v>128785517</v>
       </c>
       <c r="B27" t="n">
-        <v>92805</v>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754503</v>
+        <v>754150</v>
       </c>
       <c r="R27" t="n">
-        <v>7093050</v>
+        <v>7092826</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3362,11 +3239,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga, kapad</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,7 +3268,7 @@
         <v>128785519</v>
       </c>
       <c r="B28" t="n">
-        <v>92859</v>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,32 +3371,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128785495</v>
+        <v>128785520</v>
       </c>
       <c r="B29" t="n">
-        <v>90363</v>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3538,10 +3410,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754090</v>
+        <v>754483</v>
       </c>
       <c r="R29" t="n">
-        <v>7092862</v>
+        <v>7092966</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3580,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3603,7 +3475,7 @@
         <v>128785521</v>
       </c>
       <c r="B30" t="n">
-        <v>92859</v>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3704,7 +3576,7 @@
         <v>128785525</v>
       </c>
       <c r="B31" t="n">
-        <v>92859</v>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,7 +3677,7 @@
         <v>128785526</v>
       </c>
       <c r="B32" t="n">
-        <v>92859</v>
+        <v>93235</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3903,49 +3775,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128785520</v>
+        <v>128730804</v>
       </c>
       <c r="B33" t="n">
-        <v>92859</v>
+        <v>93181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>6055</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754483</v>
+        <v>754503</v>
       </c>
       <c r="R33" t="n">
-        <v>7092966</v>
+        <v>7093050</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3978,6 +3846,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga, kapad</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4004,52 +3877,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128785517</v>
+        <v>111674121</v>
       </c>
       <c r="B34" t="n">
-        <v>92859</v>
+        <v>90691</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Forslundaheden, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754150</v>
+        <v>754426</v>
       </c>
       <c r="R34" t="n">
-        <v>7092826</v>
+        <v>7092894</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4073,12 +3942,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4093,15 +3962,538 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128785495</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>754090</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7092862</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127946598</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>754551</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7092977</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120090197</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>754568</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7093117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120090227</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Amerika, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>754101</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7092887</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Severin Suess</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Severin Suess, Anna Becker</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127946597</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kullabäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>754551</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7092977</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42025-2024 artfynd.xlsx
+++ b/artfynd/A 42025-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674134</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674181</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674125</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674127</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674128</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674131</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674180</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674184</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120089981</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120089991</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090072</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090140</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2256,6 +2336,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090182</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2353,6 +2438,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674129</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2450,6 +2540,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674179</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128730790</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2654,6 +2754,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674123</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2751,6 +2856,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674182</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2852,6 +2962,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090190</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2953,6 +3068,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090206</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3054,6 +3174,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090216</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128730020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785517</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3368,6 +3503,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785519</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3469,6 +3609,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785520</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3570,6 +3715,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785521</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3671,6 +3821,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785525</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3772,6 +3927,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785526</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3874,6 +4034,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128730804</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3971,6 +4136,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111674121</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4072,6 +4242,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785495</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4174,6 +4349,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127946598</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4283,6 +4463,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090197</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4392,6 +4577,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120090227</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4494,8 +4684,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127946597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>